--- a/Config/Excel/monster.xlsx
+++ b/Config/Excel/monster.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29865" windowHeight="12735"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="18">
   <si>
     <t>id</t>
   </si>
@@ -37,7 +37,7 @@
     <t>name</t>
   </si>
   <si>
-    <t>prefabPath</t>
+    <t>actor</t>
   </si>
   <si>
     <t>roleType</t>
@@ -64,37 +64,25 @@
     <t>备注</t>
   </si>
   <si>
+    <t>预制体</t>
+  </si>
+  <si>
     <t>xxxx</t>
   </si>
   <si>
     <t>暗影蝙蝠</t>
   </si>
   <si>
-    <t>Assets/Bundles/Character/Actor/Monster/actor_bat</t>
-  </si>
-  <si>
     <t>红衣法师</t>
   </si>
   <si>
-    <t>Assets/Bundles/Character/Actor/Monster/actor_BOSS_wizard</t>
-  </si>
-  <si>
     <t>骷髅士兵</t>
   </si>
   <si>
-    <t>Assets/Bundles/Character/Actor/Monster/actor_skeleton</t>
-  </si>
-  <si>
     <t>绿色史莱姆</t>
   </si>
   <si>
-    <t>Assets/Bundles/Character/Actor/Monster/actor_slime</t>
-  </si>
-  <si>
     <t>蹒跚僵尸</t>
-  </si>
-  <si>
-    <t>Assets/Bundles/Character/Actor/Monster/actor_zombie</t>
   </si>
 </sst>
 </file>
@@ -717,8 +705,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1071,8 +1059,7 @@
   <dimension ref="A1:F9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
-    <col min="2" max="3" width="10.375" customWidth="1"/>
-    <col min="4" max="4" width="64.75" customWidth="1"/>
+    <col min="2" max="4" width="10.375" customWidth="1"/>
     <col min="5" max="5" width="12.25" customWidth="1"/>
     <col min="6" max="6" width="16.375" customWidth="1"/>
     <col min="7" max="7" width="10.625" customWidth="1"/>
@@ -1086,7 +1073,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1"/>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E1" t="s">
@@ -1106,7 +1093,7 @@
       <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="E2" t="s">
@@ -1126,8 +1113,8 @@
       <c r="C3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>8</v>
+      <c r="D3" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -1146,14 +1133,14 @@
       <c r="C4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>9</v>
+      <c r="D4" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1164,10 +1151,10 @@
         <v>930001</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" t="s">
         <v>13</v>
+      </c>
+      <c r="D5" s="2">
+        <v>310001</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -1183,8 +1170,8 @@
       <c r="C6" t="s">
         <v>14</v>
       </c>
-      <c r="D6" t="s">
-        <v>15</v>
+      <c r="D6" s="2">
+        <v>310002</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -1198,10 +1185,10 @@
         <v>930003</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" t="s">
-        <v>17</v>
+        <v>15</v>
+      </c>
+      <c r="D7" s="2">
+        <v>310003</v>
       </c>
       <c r="E7">
         <v>2</v>
@@ -1215,10 +1202,10 @@
         <v>930004</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" t="s">
-        <v>19</v>
+        <v>16</v>
+      </c>
+      <c r="D8" s="2">
+        <v>310004</v>
       </c>
       <c r="E8">
         <v>2</v>
@@ -1232,10 +1219,10 @@
         <v>930005</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" t="s">
-        <v>21</v>
+        <v>17</v>
+      </c>
+      <c r="D9" s="2">
+        <v>310005</v>
       </c>
       <c r="E9">
         <v>2</v>

--- a/Config/Excel/monster.xlsx
+++ b/Config/Excel/monster.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29865" windowHeight="12735"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="16">
   <si>
     <t>id</t>
   </si>
@@ -37,10 +37,7 @@
     <t>name</t>
   </si>
   <si>
-    <t>prefabPath</t>
-  </si>
-  <si>
-    <t>roleType</t>
+    <t>actorId</t>
   </si>
   <si>
     <t>headIcon</t>
@@ -70,31 +67,16 @@
     <t>暗影蝙蝠</t>
   </si>
   <si>
-    <t>Assets/Bundles/Character/Actor/Monster/actor_bat</t>
-  </si>
-  <si>
     <t>红衣法师</t>
   </si>
   <si>
-    <t>Assets/Bundles/Character/Actor/Monster/actor_BOSS_wizard</t>
-  </si>
-  <si>
     <t>骷髅士兵</t>
   </si>
   <si>
-    <t>Assets/Bundles/Character/Actor/Monster/actor_skeleton</t>
-  </si>
-  <si>
     <t>绿色史莱姆</t>
   </si>
   <si>
-    <t>Assets/Bundles/Character/Actor/Monster/actor_slime</t>
-  </si>
-  <si>
     <t>蹒跚僵尸</t>
-  </si>
-  <si>
-    <t>Assets/Bundles/Character/Actor/Monster/actor_zombie</t>
   </si>
 </sst>
 </file>
@@ -717,8 +699,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1068,17 +1050,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="3" width="10.375" customWidth="1"/>
-    <col min="4" max="4" width="64.75" customWidth="1"/>
-    <col min="5" max="5" width="12.25" customWidth="1"/>
-    <col min="6" max="6" width="16.375" customWidth="1"/>
-    <col min="7" max="7" width="10.625" customWidth="1"/>
+    <col min="2" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="16.375" customWidth="1"/>
+    <col min="6" max="6" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1086,77 +1066,63 @@
         <v>1</v>
       </c>
       <c r="C1" s="1"/>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="1" t="s">
+    <row r="3" spans="1:5">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
-      <c r="F3" t="s">
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="1"/>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:4">
       <c r="A5">
         <v>300001</v>
       </c>
@@ -1164,16 +1130,13 @@
         <v>930001</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
+        <v>11</v>
+      </c>
+      <c r="D5" s="2">
+        <v>2001</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:4">
       <c r="A6">
         <v>300002</v>
       </c>
@@ -1181,16 +1144,13 @@
         <v>930002</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
+        <v>12</v>
+      </c>
+      <c r="D6" s="2">
+        <v>2002</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:4">
       <c r="A7">
         <v>300003</v>
       </c>
@@ -1198,16 +1158,13 @@
         <v>930003</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
+        <v>13</v>
+      </c>
+      <c r="D7" s="2">
+        <v>2003</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:4">
       <c r="A8">
         <v>300004</v>
       </c>
@@ -1215,16 +1172,13 @@
         <v>930004</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8">
-        <v>2</v>
+        <v>14</v>
+      </c>
+      <c r="D8" s="2">
+        <v>2004</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:4">
       <c r="A9">
         <v>300005</v>
       </c>
@@ -1232,13 +1186,10 @@
         <v>930005</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9">
-        <v>2</v>
+        <v>15</v>
+      </c>
+      <c r="D9" s="2">
+        <v>2005</v>
       </c>
     </row>
   </sheetData>
